--- a/artfynd/A 55773-2024 artfynd.xlsx
+++ b/artfynd/A 55773-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101688537</v>
+        <v>68512572</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>1988</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kakängssundet, västra sidan Lerån, Gstr</t>
+          <t>Hyttön, SV om Lerån, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625644.2594505068</v>
+        <v>625670</v>
       </c>
       <c r="R2" t="n">
-        <v>6709037.638050094</v>
+        <v>6708963</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -747,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2017-09-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2017-09-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,16 +765,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>rel gammal naturskogsartat granskog med grönstensblock</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -792,12 +789,7 @@
         <v>101688503</v>
       </c>
       <c r="B3" t="n">
-        <v>90568</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625644.2594505068</v>
+        <v>625644</v>
       </c>
       <c r="R3" t="n">
-        <v>6709037.638050094</v>
+        <v>6709038</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,52 +894,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101688543</v>
+        <v>68512573</v>
       </c>
       <c r="B4" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>3286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kakängssundet, västra sidan Lerån, Gstr</t>
+          <t>Hyttön, SV om Lerån, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625644.2594505068</v>
+        <v>625673</v>
       </c>
       <c r="R4" t="n">
-        <v>6709037.638050094</v>
+        <v>6708965</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,22 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2017-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2017-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,68 +984,75 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>rel gammal naturskogsartat granskog med grönstensblock</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101688522</v>
+        <v>68512962</v>
       </c>
       <c r="B5" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222002</v>
+        <v>5745</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kakängssundet, västra sidan Lerån, Gstr</t>
+          <t>Hyttön, SV om Lerån, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625644.2594505068</v>
+        <v>625679</v>
       </c>
       <c r="R5" t="n">
-        <v>6709037.638050094</v>
+        <v>6708990</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,22 +1079,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2017-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2017-09-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>avser Ramaria brunneicontusa, som ej kan rapporteras (gyllenfingersvamp). R. largentii är en amerikansk art.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,19 +1100,471 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>svacka i rel gammal granskog, naturskogsartat</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>101688543</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kakängssundet, västra sidan Lerån, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>625644</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6709038</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Peter Ståhl</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Peter Ståhl</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>101688537</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kakängssundet, västra sidan Lerån, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>625644</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6709038</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>102411750</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hyttön, skogsväg S om Åängsån, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>625424</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6709146</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>XG-Gäv-2047</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>troligare 100 ex, många små</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>101688522</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kakängssundet, västra sidan Lerån, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>625644</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6709038</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55773-2024 artfynd.xlsx
+++ b/artfynd/A 55773-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68512572</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101688503</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68512573</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68512962</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101688543</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101688537</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102411750</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,8 +1605,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101688522</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>